--- a/data/trans_orig/cron_index-Edad-trans_orig.xlsx
+++ b/data/trans_orig/cron_index-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad total</t>
+          <t>Índice de cronicidad total (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,13</t>
+          <t>0,08; 0,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,42</t>
+          <t>0,17; 0,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,19</t>
+          <t>0,12; 0,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,34</t>
+          <t>0,16; 0,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,15</t>
+          <t>0,11; 0,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,18</t>
+          <t>0,12; 0,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,35</t>
+          <t>0,18; 0,34</t>
         </is>
       </c>
     </row>
@@ -876,42 +876,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,13; 0,2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,14; 0,23</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,13; 0,2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0,25; 1,09</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0,11; 0,15</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0,14; 0,2</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 0,23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,13; 0,2</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,25; 1,06</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0,11; 0,15</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 0,2</t>
-        </is>
-      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,17</t>
+          <t>0,13; 0,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,79</t>
+          <t>0,27; 0,8</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,28</t>
+          <t>0,19; 0,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 0,34</t>
+          <t>0,24; 0,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,34</t>
+          <t>0,21; 0,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,3</t>
+          <t>0,23; 0,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,78</t>
+          <t>0,24; 0,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,55</t>
+          <t>0,41; 0,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 0,77</t>
+          <t>0,58; 0,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,45; 0,56</t>
+          <t>0,44; 0,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,51</t>
+          <t>0,42; 0,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 0,73</t>
+          <t>0,38; 0,74</t>
         </is>
       </c>
     </row>
@@ -1276,22 +1276,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,17</t>
+          <t>0,95; 1,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 1,15</t>
+          <t>0,92; 1,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,06</t>
+          <t>0,81; 1,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 1,4</t>
+          <t>1,17; 1,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,22 +1301,22 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 1,41</t>
+          <t>1,14; 1,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,25</t>
+          <t>1,02; 1,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 1,29</t>
+          <t>1,1; 1,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 1,21</t>
+          <t>1,03; 1,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,14</t>
+          <t>0,95; 1,12</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,24; 1,54</t>
+          <t>1,26; 1,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,15</t>
+          <t>1,77; 2,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 1,76</t>
+          <t>1,46; 1,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 1,93</t>
+          <t>1,62; 1,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,01</t>
+          <t>1,69; 1,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,12</t>
+          <t>1,81; 2,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 1,92</t>
+          <t>1,62; 1,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,69</t>
+          <t>1,82; 2,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 1,74</t>
+          <t>1,53; 1,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,07</t>
+          <t>1,84; 2,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 1,81</t>
+          <t>1,57; 1,79</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,5</t>
+          <t>1,79; 2,53</t>
         </is>
       </c>
     </row>
@@ -1556,37 +1556,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,89</t>
+          <t>1,51; 1,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 2,34</t>
+          <t>1,97; 2,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,21</t>
+          <t>1,89; 2,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 2,64</t>
+          <t>2,27; 2,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 2,21</t>
+          <t>1,9; 2,22</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 2,56</t>
+          <t>2,23; 2,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 2,27</t>
+          <t>1,93; 2,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1596,22 +1596,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,03</t>
+          <t>1,8; 2,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,43</t>
+          <t>2,19; 2,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,96; 2,2</t>
+          <t>1,97; 2,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 2,74</t>
+          <t>2,52; 2,75</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 0,54</t>
+          <t>0,48; 0,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,67</t>
+          <t>0,58; 0,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,46</t>
+          <t>1,0; 1,45</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,19</t>
+          <t>0,9; 1,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_index-Edad-trans_orig.xlsx
+++ b/data/trans_orig/cron_index-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>0,24</t>
         </is>
       </c>
     </row>
@@ -726,32 +726,32 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,11; 0,19</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,16; 0,38</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,1; 0,16</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,1; 0,18</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>0,12; 0,19</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,17; 0,43</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 0,16</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 0,18</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,12; 0,2</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,35</t>
+          <t>0,16; 0,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,17 +761,17 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,16</t>
+          <t>0,1; 0,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,18</t>
+          <t>0,13; 0,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,34</t>
+          <t>0,18; 0,31</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,26</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,27</t>
         </is>
       </c>
     </row>
@@ -871,32 +871,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,39</t>
+          <t>0,21; 0,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,14; 0,2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,14; 0,23</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>0,13; 0,2</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 0,23</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,13; 0,2</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,09</t>
+          <t>0,22; 0,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,15</t>
+          <t>0,11; 0,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,17</t>
+          <t>0,13; 0,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 0,8</t>
+          <t>0,23; 0,33</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,34</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,27</t>
+          <t>0,19; 0,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,25</t>
+          <t>0,16; 0,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,33</t>
+          <t>0,23; 0,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,34</t>
+          <t>0,25; 0,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,34</t>
+          <t>0,28; 0,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 0,36</t>
+          <t>0,29; 0,38</t>
         </is>
       </c>
     </row>
@@ -1083,14 +1083,14 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0,74</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,54</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,53</t>
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>0,7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,72</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 0,55</t>
+          <t>0,39; 0,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 0,46</t>
+          <t>0,33; 0,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,55</t>
+          <t>0,41; 0,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,79</t>
+          <t>0,65; 0,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1161,37 +1161,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,62</t>
+          <t>0,46; 0,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,54</t>
+          <t>0,42; 0,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,77</t>
+          <t>0,63; 0,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 0,56</t>
+          <t>0,45; 0,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,51</t>
+          <t>0,41; 0,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,53</t>
+          <t>0,44; 0,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 0,74</t>
+          <t>0,66; 0,78</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,27</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>1,22</t>
         </is>
       </c>
     </row>
@@ -1276,22 +1276,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 1,19</t>
+          <t>0,94; 1,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 1,15</t>
+          <t>0,91; 1,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,06</t>
+          <t>0,82; 1,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,41</t>
+          <t>1,14; 1,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,27 +1301,27 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,4</t>
+          <t>1,15; 1,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,26</t>
+          <t>1,03; 1,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,29</t>
+          <t>1,11; 1,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,2</t>
+          <t>1,04; 1,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 1,24</t>
+          <t>1,06; 1,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 1,31</t>
+          <t>1,15; 1,3</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>1,73</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,24</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,06</t>
+          <t>1,81</t>
         </is>
       </c>
     </row>
@@ -1416,42 +1416,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 1,54</t>
+          <t>1,23; 1,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,15</t>
+          <t>1,74; 2,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 1,76</t>
+          <t>1,44; 1,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,92</t>
+          <t>1,57; 1,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 1,99</t>
+          <t>1,7; 2,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,11</t>
+          <t>1,82; 2,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,93</t>
+          <t>1,59; 1,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,65</t>
+          <t>1,77; 2,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,08</t>
+          <t>1,83; 2,08</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 1,79</t>
+          <t>1,58; 1,8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,53</t>
+          <t>1,72; 1,9</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,74</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>2,62</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,88</t>
+          <t>1,51; 1,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,39</t>
+          <t>1,94; 2,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>1,89; 2,2</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2,28; 2,69</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1,89; 2,22</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2,27; 2,64</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,9; 2,22</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,23; 2,56</t>
+          <t>2,24; 2,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,27</t>
+          <t>1,94; 2,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 2,89</t>
+          <t>2,59; 2,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,05</t>
+          <t>1,79; 2,03</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 2,43</t>
+          <t>2,18; 2,43</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,2</t>
+          <t>1,96; 2,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 2,75</t>
+          <t>2,51; 2,74</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,99</t>
+          <t>0,96</t>
         </is>
       </c>
     </row>
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,48; 0,54</t>
+          <t>0,47; 0,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,58; 0,66</t>
+          <t>0,58; 0,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,67; 0,94</t>
+          <t>0,86; 0,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 0,8</t>
+          <t>0,71; 0,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,45</t>
+          <t>0,97; 1,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,17</t>
+          <t>0,93; 0,99</t>
         </is>
       </c>
     </row>
